--- a/docs/CTRBLXAI_NonWeapon_Equipment_Export.xlsx
+++ b/docs/CTRBLXAI_NonWeapon_Equipment_Export.xlsx
@@ -814,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5935,10 +5935,79 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>── Gloves (Budget: 250 BP) ──</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>GL-021</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Initiator's Grips</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>Once per turn, the first Push action does not cost AP. That Push has RT Cost ×2 and Force ×0.5 (rounded down, minimum Force 1).</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>At first Push commitment each turn.</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>Once per turn. That Push has RT ×2 and Force ×0.5 (min 1).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A112:L112"/>
     <mergeCell ref="A90:L90"/>
     <mergeCell ref="A68:L68"/>
     <mergeCell ref="A46:L46"/>
@@ -5953,7 +6022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K412"/>
+  <dimension ref="A1:K418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -23323,14 +23392,204 @@
         <v>4</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>── Gloves ──</t>
+        </is>
+      </c>
+      <c r="B414" s="4" t="n"/>
+      <c r="C414" s="4" t="n"/>
+      <c r="D414" s="4" t="n"/>
+      <c r="E414" s="4" t="n"/>
+      <c r="F414" s="4" t="n"/>
+      <c r="G414" s="4" t="n"/>
+      <c r="H414" s="4" t="n"/>
+      <c r="I414" s="4" t="n"/>
+      <c r="J414" s="4" t="n"/>
+      <c r="K414" s="4" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GL-021</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Initiator's Grips</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="E415" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F415" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G415" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I415" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J415" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K415" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GL-021</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Initiator's Grips</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>WT</t>
+        </is>
+      </c>
+      <c r="E416" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F416" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G416" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I416" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J416" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>GL-021</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Initiator's Grips</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F417" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G417" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I417" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J417" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>GL-021</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Initiator's Grips</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="E418" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F418" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G418" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H418" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I418" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J418" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K418" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A168:K168"/>
     <mergeCell ref="A250:K250"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A86:K86"/>
     <mergeCell ref="A332:K332"/>
     <mergeCell ref="B2:K2"/>
+    <mergeCell ref="A414:K414"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
